--- a/v1/dashboard_hanh_dong_v1.xlsx
+++ b/v1/dashboard_hanh_dong_v1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pham vi va workflow" sheetId="1" r:id="R5ab03911862a497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap 30-60-90" sheetId="2" r:id="R4b71ef62a39c4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics v1" sheetId="3" r:id="R4da071a020b5458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pham vi va workflow" sheetId="1" r:id="R925f82cd90fa490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roadmap 30-60-90" sheetId="2" r:id="R3df73fd092b44c1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics v1" sheetId="3" r:id="Rc266b11e2e844dbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0%"/>
+  </x:numFmts>
   <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
@@ -40,13 +43,12 @@
     </x:font>
     <x:font>
       <x:sz val="10"/>
-      <x:color rgb="FF24313D"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FF16324F"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -59,7 +61,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF16324F"/>
+        <x:fgColor rgb="FF173653"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -69,12 +71,30 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0F766E"/>
+        <x:fgColor rgb="FF0F7B70"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="6">
+  <x:borders count="9">
     <x:border/>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:right>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:left>
+    </x:border>
     <x:border>
       <x:bottom style="thin">
         <x:color rgb="FFD8E1E8"/>
@@ -92,6 +112,12 @@
       <x:right style="thin">
         <x:color rgb="FFD8E1E8"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
@@ -100,17 +126,29 @@
       <x:right style="thin">
         <x:color rgb="FFD8E1E8"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:bottom>
     </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FFD8E1E8"/>
       </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E1E8"/>
+      </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="39">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -133,48 +171,72 @@
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -378,12 +440,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="21" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -407,9 +469,9 @@
       <x:c r="F2" s="4"/>
       <x:c r="G2" s="4"/>
     </x:row>
-    <x:row r="3" ht="34" customHeight="1">
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Bản trước phản biện, giữ lại để đối chiếu với v2.</x:v>
+        <x:v>Case Klarna AI Assistant | Bản trước phản biện, thiên về volume và cost.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -420,7 +482,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>PHẠM VI</x:v>
+        <x:v>PHẠM VI &amp; WORKFLOW V1</x:v>
       </x:c>
       <x:c r="B5" s="11"/>
       <x:c r="C5" s="11"/>
@@ -430,181 +492,179 @@
       <x:c r="G5" s="11"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="19" t="str">
+      <x:c r="A6" s="33" t="str">
         <x:v>Sản phẩm</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
-        <x:v>Trợ lý AI tra cứu tài liệu nội bộ</x:v>
-      </x:c>
-      <x:c r="C6" s="17"/>
-      <x:c r="D6" s="17"/>
-      <x:c r="E6" s="17"/>
-      <x:c r="F6" s="17"/>
-      <x:c r="G6" s="17"/>
+      <x:c r="B6" s="33" t="str">
+        <x:v>Klarna AI Assistant</x:v>
+      </x:c>
+      <x:c r="C6" s="33"/>
+      <x:c r="D6" s="33"/>
+      <x:c r="E6" s="33"/>
+      <x:c r="F6" s="33"/>
+      <x:c r="G6" s="33"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="20" t="str">
+      <x:c r="A7" s="34" t="str">
         <x:v>Người dùng</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Nhân viên vận hành</x:v>
-      </x:c>
-      <x:c r="C7" s="18"/>
-      <x:c r="D7" s="18"/>
-      <x:c r="E7" s="18"/>
-      <x:c r="F7" s="18"/>
-      <x:c r="G7" s="18"/>
+      <x:c r="B7" s="34" t="str">
+        <x:v>Khách hàng cần hỗ trợ</x:v>
+      </x:c>
+      <x:c r="C7" s="34"/>
+      <x:c r="D7" s="34"/>
+      <x:c r="E7" s="34"/>
+      <x:c r="F7" s="34"/>
+      <x:c r="G7" s="34"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="20" t="str">
+      <x:c r="A8" s="34" t="str">
         <x:v>Workflow</x:v>
       </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>Tìm → tóm tắt → kiểm chứng</x:v>
-      </x:c>
-      <x:c r="C8" s="18"/>
-      <x:c r="D8" s="18"/>
-      <x:c r="E8" s="18"/>
-      <x:c r="F8" s="18"/>
-      <x:c r="G8" s="18"/>
+      <x:c r="B8" s="34" t="str">
+        <x:v>Tiếp nhận → AI trả lời → chuyển người</x:v>
+      </x:c>
+      <x:c r="C8" s="34"/>
+      <x:c r="D8" s="34"/>
+      <x:c r="E8" s="34"/>
+      <x:c r="F8" s="34"/>
+      <x:c r="G8" s="34"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="20" t="str">
+      <x:c r="A9" s="34" t="str">
         <x:v>Vấn đề</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Ít người quay lại; vẫn tìm file và hỏi đồng nghiệp</x:v>
-      </x:c>
-      <x:c r="C9" s="18"/>
-      <x:c r="D9" s="18"/>
-      <x:c r="E9" s="18"/>
-      <x:c r="F9" s="18"/>
-      <x:c r="G9" s="18"/>
+      <x:c r="B9" s="34" t="str">
+        <x:v>Cần tăng tỷ lệ AI xử lý và giảm chi phí</x:v>
+      </x:c>
+      <x:c r="C9" s="34"/>
+      <x:c r="D9" s="34"/>
+      <x:c r="E9" s="34"/>
+      <x:c r="F9" s="34"/>
+      <x:c r="G9" s="34"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="34"/>
+      <x:c r="B10" s="34"/>
+      <x:c r="C10" s="34"/>
+      <x:c r="D10" s="34"/>
+      <x:c r="E10" s="34"/>
+      <x:c r="F10" s="34"/>
+      <x:c r="G10" s="34"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>AS-IS / TO-BE V1</x:v>
-      </x:c>
-      <x:c r="B11" s="11"/>
-      <x:c r="C11" s="11"/>
-      <x:c r="D11" s="11"/>
-      <x:c r="E11" s="11"/>
-      <x:c r="F11" s="11"/>
-      <x:c r="G11" s="11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="28" t="str">
+      <x:c r="A11" s="35" t="str">
         <x:v>AS-IS</x:v>
       </x:c>
-      <x:c r="B12" s="29" t="str">
+      <x:c r="B11" s="36" t="str">
         <x:v>Điểm đau</x:v>
       </x:c>
-      <x:c r="C12" s="29" t="str">
+      <x:c r="C11" s="36" t="str">
         <x:v>TO-BE v1</x:v>
       </x:c>
-      <x:c r="D12" s="29" t="str">
+      <x:c r="D11" s="36" t="str">
         <x:v>Nguồn</x:v>
       </x:c>
-      <x:c r="E12" s="29" t="str">
+      <x:c r="E11" s="36" t="str">
         <x:v>Người kiểm</x:v>
       </x:c>
-      <x:c r="F12" s="29" t="str">
+      <x:c r="F11" s="36" t="str">
         <x:v>Khi không chắc</x:v>
       </x:c>
-      <x:c r="G12" s="30" t="str">
+      <x:c r="G11" s="37" t="str">
         <x:v>Owner</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="48" customHeight="1">
-      <x:c r="A13" s="17" t="str">
-        <x:v>Tìm file</x:v>
-      </x:c>
-      <x:c r="B13" s="17" t="str">
-        <x:v>Nhiều thư mục</x:v>
-      </x:c>
-      <x:c r="C13" s="17" t="str">
-        <x:v>Hỏi AI</x:v>
-      </x:c>
-      <x:c r="D13" s="17" t="str">
+    <x:row r="12" ht="52" customHeight="1">
+      <x:c r="A12" s="34" t="str">
+        <x:v>Human intake</x:v>
+      </x:c>
+      <x:c r="B12" s="34" t="str">
+        <x:v>Tốn thời gian</x:v>
+      </x:c>
+      <x:c r="C12" s="34" t="str">
+        <x:v>AI tiếp nhận</x:v>
+      </x:c>
+      <x:c r="D12" s="34" t="str">
+        <x:v>FAQ/policy</x:v>
+      </x:c>
+      <x:c r="E12" s="34" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
-      <x:c r="E13" s="17" t="str">
+      <x:c r="F12" s="34" t="str">
+        <x:v>Chuyển người</x:v>
+      </x:c>
+      <x:c r="G12" s="34" t="str">
+        <x:v>AI Product</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="52" customHeight="1">
+      <x:c r="A13" s="34" t="str">
+        <x:v>Human resolve</x:v>
+      </x:c>
+      <x:c r="B13" s="34" t="str">
+        <x:v>Chi phí cao</x:v>
+      </x:c>
+      <x:c r="C13" s="34" t="str">
+        <x:v>AI trả lời</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="str">
+        <x:v>Knowledge base</x:v>
+      </x:c>
+      <x:c r="E13" s="34" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
-      <x:c r="F13" s="17" t="str">
+      <x:c r="F13" s="34" t="str">
+        <x:v>Chuyển người</x:v>
+      </x:c>
+      <x:c r="G13" s="34" t="str">
+        <x:v>AI Product</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="52" customHeight="1">
+      <x:c r="A14" s="34" t="str">
+        <x:v>Human follow-up</x:v>
+      </x:c>
+      <x:c r="B14" s="34" t="str">
+        <x:v>Khó scale</x:v>
+      </x:c>
+      <x:c r="C14" s="34" t="str">
+        <x:v>AI 24/7</x:v>
+      </x:c>
+      <x:c r="D14" s="34" t="str">
+        <x:v>Chat history</x:v>
+      </x:c>
+      <x:c r="E14" s="34" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="48" customHeight="1">
-      <x:c r="A14" s="18" t="str">
-        <x:v>Hỏi đồng nghiệp</x:v>
-      </x:c>
-      <x:c r="B14" s="18" t="str">
-        <x:v>Phụ thuộc kinh nghiệm</x:v>
-      </x:c>
-      <x:c r="C14" s="18" t="str">
-        <x:v>Đọc câu trả lời</x:v>
-      </x:c>
-      <x:c r="D14" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="E14" s="18" t="str">
-        <x:v>Người dùng</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="str">
-        <x:v>Hỏi đồng nghiệp</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="str">
-        <x:v>Người dùng</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="48" customHeight="1">
-      <x:c r="A15" s="18" t="str">
-        <x:v>Tự tóm tắt</x:v>
-      </x:c>
-      <x:c r="B15" s="18" t="str">
-        <x:v>Không nhất quán</x:v>
-      </x:c>
-      <x:c r="C15" s="18" t="str">
-        <x:v>Dùng kết quả</x:v>
-      </x:c>
-      <x:c r="D15" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="F15" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="G15" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="18" t="str">
-        <x:v>Dùng tài liệu</x:v>
-      </x:c>
-      <x:c r="B16" s="18" t="str">
-        <x:v>Khó biết bản mới nhất</x:v>
-      </x:c>
-      <x:c r="C16" s="18" t="str">
-        <x:v>Báo lỗi</x:v>
-      </x:c>
-      <x:c r="D16" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="str">
-        <x:v>Chưa rõ</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="str">
-        <x:v>Gửi chat</x:v>
-      </x:c>
-      <x:c r="G16" s="18" t="str">
-        <x:v>IT</x:v>
+      <x:c r="F14" s="34" t="str">
+        <x:v>Khách hỏi lại</x:v>
+      </x:c>
+      <x:c r="G14" s="34" t="str">
+        <x:v>CS Ops</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="52" customHeight="1">
+      <x:c r="A15" s="34" t="str">
+        <x:v>QA thủ công</x:v>
+      </x:c>
+      <x:c r="B15" s="34" t="str">
+        <x:v>Mẫu nhỏ</x:v>
+      </x:c>
+      <x:c r="C15" s="34" t="str">
+        <x:v>Theo dõi CSAT chung</x:v>
+      </x:c>
+      <x:c r="D15" s="34" t="str">
+        <x:v>Survey</x:v>
+      </x:c>
+      <x:c r="E15" s="34" t="str">
+        <x:v>QA</x:v>
+      </x:c>
+      <x:c r="F15" s="34" t="str">
+        <x:v>Review mẫu</x:v>
+      </x:c>
+      <x:c r="G15" s="34" t="str">
+        <x:v>QA</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -616,7 +676,6 @@
     <x:mergeCell ref="B7:G7"/>
     <x:mergeCell ref="B8:G8"/>
     <x:mergeCell ref="B9:G9"/>
-    <x:mergeCell ref="A11:G11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -649,9 +708,9 @@
       <x:c r="D2" s="4"/>
       <x:c r="E2" s="4"/>
     </x:row>
-    <x:row r="3" ht="34" customHeight="1">
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Bản đầu: có hoạt động và owner nhưng chưa đủ tiêu chí qua cổng.</x:v>
+        <x:v>Bản đầu có hoạt động nhưng thiếu quality gate và tiêu chí fail.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -659,70 +718,70 @@
       <x:c r="E3" s="8"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="28" t="str">
+      <x:c r="A5" s="19" t="str">
         <x:v>Giai đoạn</x:v>
       </x:c>
-      <x:c r="B5" s="29" t="str">
-        <x:v>Việc cần làm</x:v>
-      </x:c>
-      <x:c r="C5" s="29" t="str">
+      <x:c r="B5" s="20" t="str">
+        <x:v>Việc làm</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
         <x:v>Owner</x:v>
       </x:c>
-      <x:c r="D5" s="29" t="str">
+      <x:c r="D5" s="20" t="str">
         <x:v>Kết quả</x:v>
       </x:c>
-      <x:c r="E5" s="30" t="str">
+      <x:c r="E5" s="21" t="str">
         <x:v>Gate</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="17" t="str">
+    <x:row r="6" ht="60" customHeight="1">
+      <x:c r="A6" s="33" t="str">
         <x:v>0–30</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
-        <x:v>Vẽ workflow; chọn nhóm pilot; đo hiện trạng</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>AI Product Owner</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>Có bản thiết kế</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str">
+      <x:c r="B6" s="33" t="str">
+        <x:v>Thu thập số liệu volume/cost</x:v>
+      </x:c>
+      <x:c r="C6" s="33" t="str">
+        <x:v>AI Product</x:v>
+      </x:c>
+      <x:c r="D6" s="33" t="str">
+        <x:v>Có baseline</x:v>
+      </x:c>
+      <x:c r="E6" s="33" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
-      <x:c r="A7" s="18" t="str">
+    <x:row r="7" ht="60" customHeight="1">
+      <x:c r="A7" s="34" t="str">
         <x:v>31–60</x:v>
       </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Bật nguồn; QA; đào tạo người dùng</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
+      <x:c r="B7" s="34" t="str">
+        <x:v>Mở rộng AI cho nhiều intent</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="str">
         <x:v>QA Lead</x:v>
       </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Có báo cáo</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
+      <x:c r="D7" s="34" t="str">
+        <x:v>Tăng usage</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="58" customHeight="1">
-      <x:c r="A8" s="18" t="str">
+    <x:row r="8" ht="60" customHeight="1">
+      <x:c r="A8" s="34" t="str">
         <x:v>61–90</x:v>
       </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>So mục tiêu; quyết định mở rộng</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
+      <x:c r="B8" s="34" t="str">
+        <x:v>Tối ưu chi phí và scale</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="str">
         <x:v>Sponsor</x:v>
       </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>Có quyết định</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="str">
+      <x:c r="D8" s="34" t="str">
+        <x:v>Giảm cost</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="str">
         <x:v>Chưa rõ</x:v>
       </x:c>
     </x:row>
@@ -741,12 +800,13 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="31" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -760,6 +820,7 @@
       <x:c r="F1" s="4"/>
       <x:c r="G1" s="4"/>
       <x:c r="H1" s="4"/>
+      <x:c r="I1" s="4"/>
     </x:row>
     <x:row r="2" ht="15" customHeight="1">
       <x:c r="A2" s="4"/>
@@ -770,10 +831,11 @@
       <x:c r="F2" s="4"/>
       <x:c r="G2" s="4"/>
       <x:c r="H2" s="4"/>
-    </x:row>
-    <x:row r="3" ht="34" customHeight="1">
+      <x:c r="I2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="36" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>Bản đầu còn thiên về activity; đây là điểm được sửa rõ trong v2.</x:v>
+        <x:v>Các số công khai là thật nhưng bộ đo chưa đủ để ra quyết định chất lượng.</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -782,141 +844,157 @@
       <x:c r="F3" s="8"/>
       <x:c r="G3" s="8"/>
       <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="28" t="str">
+      <x:c r="A5" s="19" t="str">
         <x:v>Cấp</x:v>
       </x:c>
-      <x:c r="B5" s="29" t="str">
+      <x:c r="B5" s="20" t="str">
         <x:v>Chỉ số</x:v>
       </x:c>
-      <x:c r="C5" s="29" t="str">
+      <x:c r="C5" s="20" t="str">
         <x:v>Baseline</x:v>
       </x:c>
-      <x:c r="D5" s="29" t="str">
+      <x:c r="D5" s="20" t="str">
         <x:v>Target</x:v>
       </x:c>
-      <x:c r="E5" s="29" t="str">
+      <x:c r="E5" s="20" t="str">
+        <x:v>Kết quả</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
         <x:v>Nguồn</x:v>
       </x:c>
-      <x:c r="F5" s="29" t="str">
+      <x:c r="G5" s="20" t="str">
         <x:v>Owner</x:v>
       </x:c>
-      <x:c r="G5" s="29" t="str">
+      <x:c r="H5" s="20" t="str">
         <x:v>Khi xấu</x:v>
       </x:c>
-      <x:c r="H5" s="30" t="str">
+      <x:c r="I5" s="21" t="str">
         <x:v>Nhận xét</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="58" customHeight="1">
-      <x:c r="A6" s="17" t="str">
+    <x:row r="6" ht="62" customHeight="1">
+      <x:c r="A6" s="33" t="str">
         <x:v>Product</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="str">
-        <x:v>Số tài khoản đăng nhập</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>Đo tuần 1</x:v>
-      </x:c>
-      <x:c r="D6" s="17" t="str">
-        <x:v>Tăng 30%</x:v>
-      </x:c>
-      <x:c r="E6" s="17" t="str">
-        <x:v>Login log</x:v>
-      </x:c>
-      <x:c r="F6" s="17" t="str">
-        <x:v>AI Product Owner</x:v>
-      </x:c>
-      <x:c r="G6" s="17" t="str">
-        <x:v>Nhắc sử dụng</x:v>
-      </x:c>
-      <x:c r="H6" s="17" t="str">
-        <x:v>Activity — chưa đủ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="58" customHeight="1">
-      <x:c r="A7" s="18" t="str">
-        <x:v>Product</x:v>
-      </x:c>
-      <x:c r="B7" s="18" t="str">
-        <x:v>Số câu hỏi mỗi tuần</x:v>
-      </x:c>
-      <x:c r="C7" s="18" t="str">
-        <x:v>Đo tuần 1</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str">
-        <x:v>Tăng 50%</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="str">
-        <x:v>Chat log</x:v>
-      </x:c>
-      <x:c r="F7" s="18" t="str">
-        <x:v>AI Product Owner</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="str">
-        <x:v>Đào tạo thêm</x:v>
-      </x:c>
-      <x:c r="H7" s="18" t="str">
-        <x:v>Activity — chưa đủ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
-      <x:c r="A8" s="18" t="str">
+      <x:c r="B6" s="33" t="str">
+        <x:v>Tỷ lệ chat do AI xử lý</x:v>
+      </x:c>
+      <x:c r="C6" s="38" t="n">
+        <x:v>0.66</x:v>
+      </x:c>
+      <x:c r="D6" s="38" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E6" s="38" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="F6" s="33" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/2003292/000162828025034998/filename1.htm</x:v>
+      </x:c>
+      <x:c r="G6" s="33" t="str">
+        <x:v>AI Product</x:v>
+      </x:c>
+      <x:c r="H6" s="33" t="str">
+        <x:v>Tăng intent coverage</x:v>
+      </x:c>
+      <x:c r="I6" s="33" t="str">
+        <x:v>Usage — chưa đủ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="62" customHeight="1">
+      <x:c r="A7" s="34" t="str">
         <x:v>Workflow</x:v>
       </x:c>
-      <x:c r="B8" s="18" t="str">
-        <x:v>Thời gian tra cứu tự khai</x:v>
-      </x:c>
-      <x:c r="C8" s="18" t="str">
-        <x:v>Đo tuần 1</x:v>
-      </x:c>
-      <x:c r="D8" s="18" t="str">
-        <x:v>Giảm 20%</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="str">
-        <x:v>Khảo sát</x:v>
-      </x:c>
-      <x:c r="F8" s="18" t="str">
+      <x:c r="B7" s="34" t="str">
+        <x:v>Thời gian xử lý (phút)</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F7" s="34" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/2003292/000200329226000007/klar-20251231.htm</x:v>
+      </x:c>
+      <x:c r="G7" s="34" t="str">
         <x:v>Chủ quy trình</x:v>
       </x:c>
-      <x:c r="G8" s="18" t="str">
-        <x:v>Xem lại hướng dẫn</x:v>
-      </x:c>
-      <x:c r="H8" s="18" t="str">
-        <x:v>Nguồn tự khai</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
-      <x:c r="A9" s="18" t="str">
+      <x:c r="H7" s="34" t="str">
+        <x:v>Tối ưu retrieval</x:v>
+      </x:c>
+      <x:c r="I7" s="34" t="str">
+        <x:v>Productivity</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
+      <x:c r="A8" s="34" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="B8" s="34" t="str">
+        <x:v>Tiết kiệm chi phí (triệu USD)</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D8" s="34" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E8" s="34" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F8" s="34" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/2003292/000162828025052805/exhibit992klarnapresenta.htm</x:v>
+      </x:c>
+      <x:c r="G8" s="34" t="str">
+        <x:v>Sponsor</x:v>
+      </x:c>
+      <x:c r="H8" s="34" t="str">
+        <x:v>Rà cost-to-serve</x:v>
+      </x:c>
+      <x:c r="I8" s="34" t="str">
+        <x:v>Value nhưng thiếu quality gate</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
+      <x:c r="A9" s="34" t="str">
         <x:v>Quality</x:v>
       </x:c>
-      <x:c r="B9" s="18" t="str">
-        <x:v>Tỷ lệ câu trả lời đúng</x:v>
-      </x:c>
-      <x:c r="C9" s="18" t="str">
-        <x:v>Đo mẫu</x:v>
-      </x:c>
-      <x:c r="D9" s="18" t="str">
-        <x:v>90%</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="str">
-        <x:v>QA mẫu</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="str">
+      <x:c r="B9" s="34" t="str">
+        <x:v>CSAT tương đối</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D9" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E9" s="34" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F9" s="34" t="str">
+        <x:v>https://www.sec.gov/Archives/edgar/data/2003292/000200329226000007/klar-20251231.htm</x:v>
+      </x:c>
+      <x:c r="G9" s="34" t="str">
         <x:v>QA Lead</x:v>
       </x:c>
-      <x:c r="G9" s="18" t="str">
-        <x:v>Kiểm tra thêm</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="str">
-        <x:v>Chưa định nghĩa nguồn / citation</x:v>
+      <x:c r="H9" s="34" t="str">
+        <x:v>QA thêm</x:v>
+      </x:c>
+      <x:c r="I9" s="34" t="str">
+        <x:v>Chỉ đo trung bình, chưa theo phân khúc</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
-    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A1:I2"/>
+    <x:mergeCell ref="A3:I3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
